--- a/examples/results/Nine-stream-Linnhoff-and-Ahmad-1999-1/Solution Metrics.xlsx
+++ b/examples/results/Nine-stream-Linnhoff-and-Ahmad-1999-1/Solution Metrics.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>dTmin</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>min_dQ</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Solve Time</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ESM TAC</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Stages</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>N Recovery Units</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>N CU Units</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>N HU Units</t>
         </is>
@@ -478,26 +466,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="D2" t="n">
-        <v>43.95712184906006</v>
+        <v>98.42831134796144</v>
       </c>
       <c r="E2" t="n">
-        <v>2966548.689667022</v>
+        <v>2913909.172899047</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -509,88 +497,88 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="D3" t="n">
-        <v>36.92849373817444</v>
+        <v>68.74256801605225</v>
       </c>
       <c r="E3" t="n">
-        <v>3028352.943068301</v>
+        <v>2916917.483711772</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>1.7</v>
       </c>
       <c r="D4" t="n">
-        <v>37.02148151397705</v>
+        <v>81.45705819129944</v>
       </c>
       <c r="E4" t="n">
-        <v>2968732.051676903</v>
+        <v>2905807.275299348</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>50.75627517700195</v>
+        <v>3.135292291641235</v>
       </c>
       <c r="E5" t="n">
-        <v>2957383.324827132</v>
+        <v>2954844.749379795</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -602,57 +590,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="D6" t="n">
-        <v>44.75497913360596</v>
+        <v>103.400796175003</v>
       </c>
       <c r="E6" t="n">
-        <v>2984407.962828108</v>
+        <v>2918777.872083728</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="D7" t="n">
-        <v>27.79608249664307</v>
+        <v>83.78581929206848</v>
       </c>
       <c r="E7" t="n">
-        <v>2912412.364663706</v>
+        <v>2913910.717723281</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
@@ -664,26 +652,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="D8" t="n">
-        <v>36.43878865242004</v>
+        <v>85.03760027885437</v>
       </c>
       <c r="E8" t="n">
-        <v>2985137.755458789</v>
+        <v>2951798.177648552</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -695,26 +683,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="D9" t="n">
-        <v>38.14692783355713</v>
+        <v>56.11359882354736</v>
       </c>
       <c r="E9" t="n">
-        <v>2975802.566814198</v>
+        <v>2962004.159444098</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
@@ -726,26 +714,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="D10" t="n">
-        <v>36.25356340408325</v>
+        <v>64.41504907608032</v>
       </c>
       <c r="E10" t="n">
-        <v>2971909.227882145</v>
+        <v>2947465.357060617</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
@@ -757,26 +745,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>89.20865631103516</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2952907.608621235</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
         <v>12</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>41.70362091064453</v>
-      </c>
-      <c r="E11" t="n">
-        <v>3503793.749207285</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" t="n">
-        <v>8</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -788,88 +776,88 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>92.00741839408876</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2941030.591187407</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
         <v>12</v>
       </c>
-      <c r="C12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>46.15046811103821</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2909975.798767159</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="n">
-        <v>8</v>
-      </c>
       <c r="H12" t="n">
         <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="D13" t="n">
-        <v>61.33078742027283</v>
+        <v>74.53262615203857</v>
       </c>
       <c r="E13" t="n">
-        <v>2936537.298891445</v>
+        <v>2956970.452918245</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>93.35440897941589</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2938956.140354879</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
         <v>12</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>55.23374938964844</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2967837.152121474</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4</v>
-      </c>
-      <c r="G14" t="n">
-        <v>13</v>
       </c>
       <c r="H14" t="n">
         <v>3</v>
@@ -881,26 +869,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>56.51584053039551</v>
+        <v>78.70490527153015</v>
       </c>
       <c r="E15" t="n">
-        <v>2950672.771483212</v>
+        <v>2943750.108864363</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
@@ -912,20 +900,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="D16" t="n">
-        <v>59.98076200485229</v>
+        <v>98.59754800796507</v>
       </c>
       <c r="E16" t="n">
-        <v>2976585.447775985</v>
+        <v>2948997.710507261</v>
       </c>
       <c r="F16" t="n">
         <v>4</v>
@@ -943,119 +931,119 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="D17" t="n">
-        <v>29.38087487220764</v>
+        <v>92.8764190673828</v>
       </c>
       <c r="E17" t="n">
-        <v>2909551.015756666</v>
+        <v>2972152.664630221</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H17" t="n">
         <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="D18" t="n">
-        <v>37.55456447601318</v>
+        <v>97.34224224090576</v>
       </c>
       <c r="E18" t="n">
-        <v>2908182.087786533</v>
+        <v>3030273.064585414</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="D19" t="n">
-        <v>75.1412935256958</v>
+        <v>130.0759680271149</v>
       </c>
       <c r="E19" t="n">
-        <v>2972972.870772304</v>
+        <v>2967291.807896431</v>
       </c>
       <c r="F19" t="n">
         <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H19" t="n">
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="D20" t="n">
-        <v>55.08447456359863</v>
+        <v>69.01097583770752</v>
       </c>
       <c r="E20" t="n">
-        <v>2947830.227624712</v>
+        <v>2963812.84267723</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
@@ -1067,20 +1055,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="D21" t="n">
-        <v>1.558583736419678</v>
+        <v>77.42089200019836</v>
       </c>
       <c r="E21" t="n">
-        <v>2976976.976491268</v>
+        <v>2979242.785644533</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
@@ -1092,32 +1080,32 @@
         <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="D22" t="n">
-        <v>49.62456655502319</v>
+        <v>60.46452593803406</v>
       </c>
       <c r="E22" t="n">
-        <v>2907176.178781828</v>
+        <v>2946660.300347254</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H22" t="n">
         <v>3</v>
@@ -1129,26 +1117,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
         <v>2.4</v>
       </c>
       <c r="D23" t="n">
-        <v>45.31535220146179</v>
+        <v>77.52404189109802</v>
       </c>
       <c r="E23" t="n">
-        <v>2904425.229444846</v>
+        <v>2963934.37203405</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
         <v>3</v>
@@ -1160,26 +1148,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="D24" t="n">
-        <v>35.116450548172</v>
+        <v>29.62619686126709</v>
       </c>
       <c r="E24" t="n">
-        <v>2939997.505402862</v>
+        <v>3564528.393510576</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
         <v>3</v>
@@ -1191,57 +1179,57 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D25" t="n">
-        <v>40.65756058692932</v>
+        <v>74.19345903396606</v>
       </c>
       <c r="E25" t="n">
-        <v>2949834.617130169</v>
+        <v>2914004.160475116</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
         <v>3</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>8</v>
       </c>
       <c r="C26" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="D26" t="n">
-        <v>32.07847428321838</v>
+        <v>74.06494092941284</v>
       </c>
       <c r="E26" t="n">
-        <v>2963698.010421236</v>
+        <v>2969889.825037167</v>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
@@ -1253,7 +1241,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1263,10 +1251,10 @@
         <v>1.3</v>
       </c>
       <c r="D27" t="n">
-        <v>38.82157516479492</v>
+        <v>98.34157156944276</v>
       </c>
       <c r="E27" t="n">
-        <v>2963934.372281325</v>
+        <v>2942311.201058172</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -1284,20 +1272,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>8</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>36.96207571029663</v>
+        <v>57.76945376396179</v>
       </c>
       <c r="E28" t="n">
-        <v>2970256.861927068</v>
+        <v>3053657.213357564</v>
       </c>
       <c r="F28" t="n">
         <v>3</v>
@@ -1309,29 +1297,29 @@
         <v>3</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C29" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="D29" t="n">
-        <v>45.20439100265503</v>
+        <v>21.42613768577576</v>
       </c>
       <c r="E29" t="n">
-        <v>2922673.529408169</v>
+        <v>2965414.046584185</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>11</v>
@@ -1346,181 +1334,181 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="D30" t="n">
-        <v>29.58569002151489</v>
+        <v>60.93026518821716</v>
       </c>
       <c r="E30" t="n">
-        <v>2971398.120806464</v>
+        <v>2911054.604001431</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H30" t="n">
         <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C31" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="D31" t="n">
-        <v>39.19372344017029</v>
+        <v>31.64232397079468</v>
       </c>
       <c r="E31" t="n">
-        <v>2951954.186179273</v>
+        <v>2921673.338196637</v>
       </c>
       <c r="F31" t="n">
         <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H31" t="n">
         <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C32" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="D32" t="n">
-        <v>27.02902460098267</v>
+        <v>32.92536687850952</v>
       </c>
       <c r="E32" t="n">
-        <v>3055637.992544006</v>
+        <v>2974198.101498944</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
         <v>3</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C33" t="n">
         <v>2.1</v>
       </c>
       <c r="D33" t="n">
-        <v>52.20106339454651</v>
+        <v>32.09751677513123</v>
       </c>
       <c r="E33" t="n">
-        <v>2941064.511844886</v>
+        <v>3032167.108015074</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H33" t="n">
         <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C34" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="D34" t="n">
-        <v>30.2906551361084</v>
+        <v>50.02915906906128</v>
       </c>
       <c r="E34" t="n">
-        <v>2966504.683266315</v>
+        <v>2974879.498478174</v>
       </c>
       <c r="F34" t="n">
         <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
         <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="D35" t="n">
-        <v>16.06265330314636</v>
+        <v>49.3899462223053</v>
       </c>
       <c r="E35" t="n">
-        <v>3059448.193396446</v>
+        <v>2917052.020796607</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H35" t="n">
         <v>3</v>
@@ -1532,57 +1520,57 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="D36" t="n">
-        <v>34.36399006843567</v>
+        <v>73.96709179878235</v>
       </c>
       <c r="E36" t="n">
-        <v>2952411.898167127</v>
+        <v>2915498.158397096</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H36" t="n">
         <v>3</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="D37" t="n">
-        <v>30.04240441322327</v>
+        <v>103.8146350383758</v>
       </c>
       <c r="E37" t="n">
-        <v>2974485.945599184</v>
+        <v>2969975.357817184</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H37" t="n">
         <v>3</v>
@@ -1594,119 +1582,119 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="D38" t="n">
-        <v>13.88428854942322</v>
+        <v>99.17324805259705</v>
       </c>
       <c r="E38" t="n">
-        <v>2930953.066994256</v>
+        <v>2970743.956774028</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H38" t="n">
         <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="D39" t="n">
-        <v>18.17398595809937</v>
+        <v>93.95961785316469</v>
       </c>
       <c r="E39" t="n">
-        <v>3041370.161577279</v>
+        <v>2981822.519205816</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C40" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>15.797203540802</v>
+        <v>86.73981237411499</v>
       </c>
       <c r="E40" t="n">
-        <v>2946792.05188624</v>
+        <v>2952407.661974077</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G40" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H40" t="n">
         <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="D41" t="n">
-        <v>29.74161100387573</v>
+        <v>67.07477307319641</v>
       </c>
       <c r="E41" t="n">
-        <v>2963934.370934132</v>
+        <v>2950461.123718428</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H41" t="n">
         <v>3</v>
@@ -1718,23 +1706,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="D42" t="n">
-        <v>25.90011954307556</v>
+        <v>182.2303321361541</v>
       </c>
       <c r="E42" t="n">
-        <v>2980137.066296232</v>
+        <v>2921283.739119653</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" t="n">
         <v>11</v>
@@ -1749,26 +1737,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C43" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="D43" t="n">
-        <v>21.34621095657349</v>
+        <v>97.21035718917848</v>
       </c>
       <c r="E43" t="n">
-        <v>2963135.653884778</v>
+        <v>2968835.768914848</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H43" t="n">
         <v>3</v>
@@ -1780,54 +1768,54 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="D44" t="n">
-        <v>12.28346538543701</v>
+        <v>132.9025011062622</v>
       </c>
       <c r="E44" t="n">
-        <v>2998157.954813076</v>
+        <v>3043247.579699235</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H44" t="n">
         <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="D45" t="n">
-        <v>30.76324987411499</v>
+        <v>73.30218029022217</v>
       </c>
       <c r="E45" t="n">
-        <v>2960840.755525041</v>
+        <v>2967203.949453262</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
         <v>9</v>
@@ -1836,32 +1824,32 @@
         <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C46" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="D46" t="n">
-        <v>109.2535126209259</v>
+        <v>91.32476282119752</v>
       </c>
       <c r="E46" t="n">
-        <v>2922863.83111635</v>
+        <v>2953585.921484292</v>
       </c>
       <c r="F46" t="n">
         <v>4</v>
       </c>
       <c r="G46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H46" t="n">
         <v>3</v>
@@ -1873,88 +1861,88 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C47" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="D47" t="n">
-        <v>24.05959630012512</v>
+        <v>77.16799306869507</v>
       </c>
       <c r="E47" t="n">
-        <v>2910025.946889923</v>
+        <v>2954074.899317275</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>72.59206581115723</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2963240.588266106</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" t="n">
         <v>10</v>
       </c>
-      <c r="C48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D48" t="n">
-        <v>34.95674896240234</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2916546.065222943</v>
-      </c>
-      <c r="F48" t="n">
-        <v>3</v>
-      </c>
-      <c r="G48" t="n">
-        <v>9</v>
-      </c>
       <c r="H48" t="n">
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.380012035369873</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2951970.501239211</v>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
         <v>10</v>
-      </c>
-      <c r="C49" t="n">
-        <v>4</v>
-      </c>
-      <c r="D49" t="n">
-        <v>22.01020073890686</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2967553.970903979</v>
-      </c>
-      <c r="F49" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" t="n">
-        <v>6</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
@@ -1966,26 +1954,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D50" t="n">
-        <v>28.40947890281677</v>
+        <v>67.83152651786804</v>
       </c>
       <c r="E50" t="n">
-        <v>2950310.60533284</v>
+        <v>2957348.931345569</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H50" t="n">
         <v>3</v>
@@ -1997,57 +1985,57 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D51" t="n">
+        <v>55.34782719612122</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2957912.191212529</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" t="n">
         <v>10</v>
       </c>
-      <c r="C51" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D51" t="n">
-        <v>28.15573048591614</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2976784.706099473</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" t="n">
-        <v>9</v>
-      </c>
       <c r="H51" t="n">
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>42.42074847221375</v>
+        <v>62.88130331039429</v>
       </c>
       <c r="E52" t="n">
-        <v>3022075.42664353</v>
+        <v>3026006.861652859</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H52" t="n">
         <v>3</v>
@@ -2059,26 +2047,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>10</v>
       </c>
       <c r="C53" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="D53" t="n">
-        <v>37.17891693115234</v>
+        <v>57.77638220787048</v>
       </c>
       <c r="E53" t="n">
-        <v>2949416.680698779</v>
+        <v>2980137.066296233</v>
       </c>
       <c r="F53" t="n">
         <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H53" t="n">
         <v>3</v>
@@ -2090,26 +2078,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="D54" t="n">
-        <v>107.2665014266968</v>
+        <v>65.4155421257019</v>
       </c>
       <c r="E54" t="n">
-        <v>3053345.781386624</v>
+        <v>2957912.191212529</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H54" t="n">
         <v>3</v>
@@ -2121,29 +2109,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C55" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="D55" t="n">
-        <v>25.72286367416382</v>
+        <v>94.60838484764101</v>
       </c>
       <c r="E55" t="n">
-        <v>3014791.054259107</v>
+        <v>2964493.553324607</v>
       </c>
       <c r="F55" t="n">
         <v>4</v>
       </c>
       <c r="G55" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
         <v>2</v>
@@ -2152,23 +2140,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="D56" t="n">
-        <v>26.40406894683838</v>
+        <v>67.35349202156067</v>
       </c>
       <c r="E56" t="n">
-        <v>2908544.539834446</v>
+        <v>2950310.603548774</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56" t="n">
         <v>8</v>
@@ -2177,60 +2165,60 @@
         <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C57" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D57" t="n">
-        <v>105.3754675388336</v>
+        <v>65.60803198814392</v>
       </c>
       <c r="E57" t="n">
-        <v>2952364.268970913</v>
+        <v>2950310.603548774</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H57" t="n">
         <v>3</v>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="D58" t="n">
-        <v>113.680597782135</v>
+        <v>68.89800310134888</v>
       </c>
       <c r="E58" t="n">
-        <v>2972509.386912291</v>
+        <v>2950310.603548774</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G58" t="n">
         <v>8</v>
@@ -2245,26 +2233,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C59" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="D59" t="n">
-        <v>91.21988606452942</v>
+        <v>77.61917591094971</v>
       </c>
       <c r="E59" t="n">
-        <v>2962425.002631108</v>
+        <v>2976622.655865763</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G59" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H59" t="n">
         <v>3</v>
@@ -2276,26 +2264,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="D60" t="n">
-        <v>21.69112205505371</v>
+        <v>2.053057432174683</v>
       </c>
       <c r="E60" t="n">
-        <v>2961952.572291888</v>
+        <v>2954184.084197724</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H60" t="n">
         <v>3</v>
@@ -2307,26 +2295,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C61" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="D61" t="n">
-        <v>130.8562643527985</v>
+        <v>73.24769806861877</v>
       </c>
       <c r="E61" t="n">
-        <v>2976980.006633233</v>
+        <v>2950310.605332839</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G61" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H61" t="n">
         <v>3</v>
@@ -2338,57 +2326,57 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C62" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="D62" t="n">
-        <v>1.015069007873535</v>
+        <v>109.5488650798798</v>
       </c>
       <c r="E62" t="n">
-        <v>2966116.036326631</v>
+        <v>2946493.031118435</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
       </c>
       <c r="G62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H62" t="n">
         <v>3</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C63" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>127.9672560691833</v>
+        <v>69.85133099555969</v>
       </c>
       <c r="E63" t="n">
-        <v>2964683.541124962</v>
+        <v>2947599.752397469</v>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H63" t="n">
         <v>3</v>
@@ -2400,88 +2388,88 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C64" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="D64" t="n">
-        <v>1.020342111587524</v>
+        <v>70.97444796562195</v>
       </c>
       <c r="E64" t="n">
-        <v>2966116.036326631</v>
+        <v>2947599.754642829</v>
       </c>
       <c r="F64" t="n">
         <v>3</v>
       </c>
       <c r="G64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H64" t="n">
         <v>3</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="D65" t="n">
-        <v>17.37360429763794</v>
+        <v>0.991384983062744</v>
       </c>
       <c r="E65" t="n">
-        <v>3615514.173029632</v>
+        <v>2948694.106145236</v>
       </c>
       <c r="F65" t="n">
         <v>4</v>
       </c>
       <c r="G65" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H65" t="n">
         <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="D66" t="n">
-        <v>147.5415365695953</v>
+        <v>1.294368982315064</v>
       </c>
       <c r="E66" t="n">
-        <v>3007976.972234316</v>
+        <v>2963413.062138585</v>
       </c>
       <c r="F66" t="n">
         <v>5</v>
       </c>
       <c r="G66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H66" t="n">
         <v>3</v>
@@ -2493,51 +2481,51 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C67" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="D67" t="n">
-        <v>17.94774055480957</v>
+        <v>94.3248336315155</v>
       </c>
       <c r="E67" t="n">
-        <v>2996297.934860545</v>
+        <v>2946708.695349619</v>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H67" t="n">
         <v>3</v>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="D68" t="n">
-        <v>129.4270341396332</v>
+        <v>0.9722232818603516</v>
       </c>
       <c r="E68" t="n">
-        <v>2956346.795573363</v>
+        <v>2960003.669804043</v>
       </c>
       <c r="F68" t="n">
         <v>5</v>
@@ -2549,32 +2537,32 @@
         <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C69" t="n">
         <v>1.3</v>
       </c>
       <c r="D69" t="n">
-        <v>19.63747549057007</v>
+        <v>0.8290431499481201</v>
       </c>
       <c r="E69" t="n">
-        <v>2974624.334574465</v>
+        <v>2957248.696393365</v>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H69" t="n">
         <v>3</v>
@@ -2586,32 +2574,94 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>25/08/2025 16:10:14</t>
+          <t>15/06/2026 15:37:28</t>
         </is>
       </c>
       <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.9405813217163086</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3057825.598823539</v>
+      </c>
+      <c r="F70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G70" t="n">
+        <v>7</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>15/06/2026 15:37:28</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1.410811424255371</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2982158.600762303</v>
+      </c>
+      <c r="F71" t="n">
+        <v>5</v>
+      </c>
+      <c r="G71" t="n">
         <v>12</v>
       </c>
-      <c r="C70" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D70" t="n">
-        <v>29.06350135803223</v>
-      </c>
-      <c r="E70" t="n">
-        <v>2906560.96896744</v>
-      </c>
-      <c r="F70" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" t="n">
-        <v>8</v>
-      </c>
-      <c r="H70" t="n">
-        <v>3</v>
-      </c>
-      <c r="I70" t="n">
-        <v>3</v>
+      <c r="H71" t="n">
+        <v>3</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>15/06/2026 15:37:28</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.758803129196167</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2963951.212860459</v>
+      </c>
+      <c r="F72" t="n">
+        <v>5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>11</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
